--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0003T0006Z000C1N74_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0003T0006Z000C1N74_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>55.13674165196137</v>
+        <v>8.959720518443723</v>
       </c>
       <c r="D2" t="n">
-        <v>14.14896258957211</v>
+        <v>2.299206420805469</v>
       </c>
       <c r="E2" t="n">
-        <v>10.80142570737659</v>
+        <v>1.755231677448697</v>
       </c>
       <c r="F2" t="n">
-        <v>8.185833190835384</v>
+        <v>1.33019789351075</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>37.43293251572252</v>
+        <v>6.082851533804909</v>
       </c>
       <c r="D3" t="n">
-        <v>4.716990566028302</v>
+        <v>0.7665109669795991</v>
       </c>
       <c r="E3" t="n">
-        <v>10.80142570737659</v>
+        <v>1.755231677448697</v>
       </c>
       <c r="F3" t="n">
-        <v>8.185833190835384</v>
+        <v>1.33019789351075</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>29.25692046275728</v>
+        <v>4.754249575198058</v>
       </c>
       <c r="D4" t="n">
-        <v>24.75661258356382</v>
+        <v>4.022949544829121</v>
       </c>
       <c r="E4" t="n">
-        <v>10.80142570737659</v>
+        <v>1.755231677448697</v>
       </c>
       <c r="F4" t="n">
-        <v>8.185833190835384</v>
+        <v>1.33019789351075</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
